--- a/01_analyses_states/Himachal Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Himachal Pradesh/results/SoIB_summaries.xlsx
@@ -402,7 +402,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -434,13 +434,13 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>33.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C8">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="3">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Himachal Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Himachal Pradesh/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -440,7 +440,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>33.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C8">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Himachal Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Himachal Pradesh/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>75</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -491,7 +491,7 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="C8">
-        <v>442</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>507</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>71.8</v>
+        <v>72.8</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E2">
-        <v>78.7</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>28.2</v>
+        <v>27.2</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
     </row>
   </sheetData>
